--- a/outputs/Timetable.xlsx
+++ b/outputs/Timetable.xlsx
@@ -4,23 +4,42 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="CSEA-I" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="CSEB-I" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Legend" state="visible" r:id="rId6"/>
+    <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="CSEA-I" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="CSEB-I" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Legend" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="58">
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Total Courses</t>
+  </si>
+  <si>
+    <t>Total Weekly Hours</t>
+  </si>
+  <si>
+    <t>Shared Faculty Courses</t>
+  </si>
+  <si>
+    <t>CSEA-I</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>CSEB-I</t>
+  </si>
   <si>
     <t>Day \ Slot</t>
   </si>
   <si>
-    <t>8:00-8:55</t>
-  </si>
-  <si>
     <t>9:00-9:55</t>
   </si>
   <si>
@@ -30,13 +49,22 @@
     <t>11:00-11:55</t>
   </si>
   <si>
-    <t>1:00-1:55</t>
+    <t>12:00-12:55</t>
+  </si>
+  <si>
+    <t>Lunch Break</t>
   </si>
   <si>
     <t>2:00-2:55</t>
   </si>
   <si>
     <t>3:00-3:55</t>
+  </si>
+  <si>
+    <t>4:00-4:55</t>
+  </si>
+  <si>
+    <t>5:00-5:55</t>
   </si>
   <si>
     <t>Monday</t>
@@ -44,17 +72,17 @@
   <si>
     <t xml:space="preserve">CS104
 F02
-Room 101</t>
+Room C104</t>
   </si>
   <si>
     <t xml:space="preserve">CS101
 F01
-Room 101</t>
+Room C105</t>
   </si>
   <si>
     <t xml:space="preserve">CS101
 F01
-Lab 201</t>
+Lab L106</t>
   </si>
   <si>
     <t>Tuesday</t>
@@ -62,20 +90,20 @@
   <si>
     <t xml:space="preserve">CS102
 F04
-Room 101</t>
+Room C105</t>
   </si>
   <si>
     <t xml:space="preserve">CS103
 F03
-Room 101</t>
-  </si>
-  <si>
-    <t>Wednesday</t>
+Room C105</t>
   </si>
   <si>
     <t xml:space="preserve">CS103
 F03
-Lab 201</t>
+Lab L105</t>
+  </si>
+  <si>
+    <t>Wednesday</t>
   </si>
   <si>
     <t/>
@@ -89,37 +117,27 @@
   <si>
     <t xml:space="preserve">CS104
 F02
-Room 102</t>
+Room C105</t>
   </si>
   <si>
     <t xml:space="preserve">CS102
 F04
-Room 102</t>
+Room C106</t>
   </si>
   <si>
     <t xml:space="preserve">CS105
 F05
-Room 101</t>
+Room C105</t>
   </si>
   <si>
     <t xml:space="preserve">CS101
 F01
-Room 102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS101
-F01
-Lab 202</t>
+Room C106</t>
   </si>
   <si>
     <t xml:space="preserve">CS105
 F05
-Lab 202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS105
-F05
-Lab 201</t>
+Lab L106</t>
   </si>
   <si>
     <t>Course Code</t>
@@ -134,6 +152,9 @@
     <t>Sessions per week</t>
   </si>
   <si>
+    <t>Room Requirements</t>
+  </si>
+  <si>
     <t>Color</t>
   </si>
   <si>
@@ -146,6 +167,9 @@
     <t>F02</t>
   </si>
   <si>
+    <t>Computers</t>
+  </si>
+  <si>
     <t>CS101</t>
   </si>
   <si>
@@ -164,6 +188,9 @@
     <t>F04</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>CS103</t>
   </si>
   <si>
@@ -171,6 +198,9 @@
   </si>
   <si>
     <t>F03</t>
+  </si>
+  <si>
+    <t>Hardware</t>
   </si>
   <si>
     <t>CS105</t>
@@ -260,10 +290,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -625,168 +655,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="8" width="18" customWidth="1"/>
+    <col min="1" max="2" width="15" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="B2" s="2">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="5"/>
-    </row>
-    <row r="3" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>17</v>
+      <c r="B3" s="2">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -794,167 +712,203 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="8" width="18" customWidth="1"/>
+    <col min="2" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="B2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="H2" s="5"/>
+      <c r="I2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="5"/>
+    </row>
+    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="F3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="G3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5" t="s">
+      <c r="I3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="8" t="s">
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="8"/>
-      <c r="H4" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>17</v>
+      <c r="B4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -963,116 +917,339 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="10" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="5"/>
+      <c r="J3" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="4" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D2">
         <v>2</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D3">
         <v>12</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D4">
         <v>8</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D5">
         <v>5</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D6">
         <v>6</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>17</v>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Timetable.xlsx
+++ b/outputs/Timetable.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Summary" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="CSEA-I" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="CSEB-I" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Legend" state="visible" r:id="rId7"/>
+    <sheet sheetId="2" name="CSE-VI" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="DSAI-VI" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="ECE-VI" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Legend" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="121">
   <si>
     <t>Section</t>
   </si>
@@ -28,149 +29,167 @@
     <t>Shared Faculty Courses</t>
   </si>
   <si>
-    <t>CSEA-I</t>
+    <t>CSE-VI</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>CSEB-I</t>
+    <t>DSAI-VI</t>
+  </si>
+  <si>
+    <t>ECE-VI</t>
   </si>
   <si>
     <t>Day \ Slot</t>
   </si>
   <si>
-    <t>9:00-10:00</t>
-  </si>
-  <si>
-    <t>9:00-10:30</t>
-  </si>
-  <si>
-    <t>10:45-11:45</t>
-  </si>
-  <si>
-    <t>10:45-12:15</t>
-  </si>
-  <si>
-    <t>12:30-1:30</t>
-  </si>
-  <si>
-    <t>12:30-2:00</t>
-  </si>
-  <si>
-    <t>2:15-3:15</t>
-  </si>
-  <si>
-    <t>2:15-3:45</t>
+    <t>8:00-9:00</t>
+  </si>
+  <si>
+    <t>8:00-9:30</t>
+  </si>
+  <si>
+    <t>9:45-10:45</t>
+  </si>
+  <si>
+    <t>9:45-11:15</t>
+  </si>
+  <si>
+    <t>11:30-12:30</t>
   </si>
   <si>
     <t>Lunch Break</t>
   </si>
   <si>
-    <t>5:00-6:00</t>
+    <t>2:00-3:00</t>
+  </si>
+  <si>
+    <t>2:00-3:30</t>
+  </si>
+  <si>
+    <t>3:45-4:45</t>
+  </si>
+  <si>
+    <t>3:45-5:15</t>
   </si>
   <si>
     <t>Monday</t>
   </si>
   <si>
-    <t xml:space="preserve">CS104 (1hr)
-F02
-Room 101</t>
+    <t xml:space="preserve">EC456 (1hr)
+undefined
+undefined</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t xml:space="preserve">CS101 (1.5hr)
-F01
-Room 101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS101 (1hr)
-F01
-Room 101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS101 (1.5hr)
-F01
-Lab 201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS102 (1hr)
-F04
-Room 101</t>
+    <t xml:space="preserve">CS469 (1hr)
+undefined
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS205 (1hr)
+undefined
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASD351 (1hr)
+undefined
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS351 (1hr)
+undefined
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS308 (1.5hr)
+F050
+undefined</t>
   </si>
   <si>
     <t>Tuesday</t>
   </si>
   <si>
-    <t xml:space="preserve">CS102 (1.5hr)
-F04
-Room 101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS103 (1.5hr)
-F03
-Room 101</t>
+    <t xml:space="preserve">DS308 (1hr)
+F050
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS308 (1hr)
+TBA
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DS308 (1.5hr)
+TBA
+undefined</t>
   </si>
   <si>
     <t>Wednesday</t>
   </si>
   <si>
-    <t xml:space="preserve">CS103 (1.5hr)
-F03
-Hardware Lab 101</t>
+    <t xml:space="preserve">EC456 (1.5hr)
+TBA
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC456 (1hr)
+TBA
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS368 (1.5hr)
+TBA
+undefined</t>
   </si>
   <si>
     <t>Thursday</t>
   </si>
   <si>
+    <t xml:space="preserve">CS368 (1hr)
+TBA
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS369 (1.5hr)
+TBA
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS369 (1hr)
+TBA
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC363 (1.5hr)
+TBA
+undefined</t>
+  </si>
+  <si>
     <t>Friday</t>
   </si>
   <si>
-    <t xml:space="preserve">CS104 (1hr)
-F02
-Room 102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS102 (1.5hr)
-F04
-Room 102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS102 (1hr)
-F04
-Room 102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS105 (1.5hr)
-F05
-Room 101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS101 (1hr)
-F01
-Room 102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS101 (1.5hr)
-F01
-Room 102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS105 (1hr)
-F05
-Room 101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS105 (1.5hr)
-F05
-Room 102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CS105 (1.5hr)
-F05
-Lab 201</t>
+    <t xml:space="preserve">EC363 (1hr)
+TBA
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS370 (1hr)
+TBA
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS370 (1.5hr)
+TBA
+undefined</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC307 (1.5hr)
+F012
+undefined</t>
   </si>
   <si>
     <t>Course Code</t>
@@ -191,73 +210,214 @@
     <t>Color</t>
   </si>
   <si>
-    <t>CS104</t>
-  </si>
-  <si>
-    <t>Web Dev Elective</t>
-  </si>
-  <si>
-    <t>F02</t>
+    <t>EC456</t>
+  </si>
+  <si>
+    <t>Reinforcement Learning</t>
+  </si>
+  <si>
+    <t>9 (11.0hr)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CS368</t>
+  </si>
+  <si>
+    <t>Computer Architecture for AI Systems</t>
+  </si>
+  <si>
+    <t>6 (7.0hr)</t>
+  </si>
+  <si>
+    <t>CS369</t>
+  </si>
+  <si>
+    <t>Software Design and Architecture</t>
+  </si>
+  <si>
+    <t>EC363</t>
+  </si>
+  <si>
+    <t>CMOS RF Circuit Design</t>
+  </si>
+  <si>
+    <t>CS370</t>
+  </si>
+  <si>
+    <t>Remote Sensing and Applications</t>
+  </si>
+  <si>
+    <t>5 (6.0hr)</t>
+  </si>
+  <si>
+    <t>CS371</t>
+  </si>
+  <si>
+    <t>GPU Computing</t>
+  </si>
+  <si>
+    <t>3 (3.0hr)</t>
+  </si>
+  <si>
+    <t>DA351</t>
+  </si>
+  <si>
+    <t>Explainable AI</t>
   </si>
   <si>
     <t>2 (2.0hr)</t>
   </si>
   <si>
-    <t>Computers</t>
-  </si>
-  <si>
-    <t>CS101</t>
-  </si>
-  <si>
-    <t>Data Structures</t>
-  </si>
-  <si>
-    <t>F01</t>
-  </si>
-  <si>
-    <t>8 (11.0hr)</t>
-  </si>
-  <si>
-    <t>CS102</t>
-  </si>
-  <si>
-    <t>Discrete Math</t>
-  </si>
-  <si>
-    <t>F04</t>
-  </si>
-  <si>
-    <t>6 (8.0hr)</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>CS103</t>
-  </si>
-  <si>
-    <t>Digital Logic</t>
-  </si>
-  <si>
-    <t>F03</t>
+    <t>CS469</t>
+  </si>
+  <si>
+    <t>Virtualisation and Cloud Computing</t>
+  </si>
+  <si>
+    <t>CS372</t>
+  </si>
+  <si>
+    <t>Biometric Security and Forensics</t>
+  </si>
+  <si>
+    <t>CS472</t>
+  </si>
+  <si>
+    <t>Bioinformatics</t>
+  </si>
+  <si>
+    <t>CS464</t>
+  </si>
+  <si>
+    <t>Deep Learning for Computer Vision</t>
+  </si>
+  <si>
+    <t>EC366</t>
+  </si>
+  <si>
+    <t>Device-Circuit Co-Design</t>
+  </si>
+  <si>
+    <t>CS205</t>
+  </si>
+  <si>
+    <t>Graph Theory</t>
+  </si>
+  <si>
+    <t>CS455</t>
+  </si>
+  <si>
+    <t>Blockchain Technology</t>
+  </si>
+  <si>
+    <t>CS458</t>
+  </si>
+  <si>
+    <t>Natural Language Processing</t>
+  </si>
+  <si>
+    <t>EC367</t>
+  </si>
+  <si>
+    <t>Industrial IoT</t>
+  </si>
+  <si>
+    <t>ASD351</t>
+  </si>
+  <si>
+    <t>Design Thinking and Innovation</t>
+  </si>
+  <si>
+    <t>DA352</t>
+  </si>
+  <si>
+    <t>Full Stack Development II</t>
+  </si>
+  <si>
+    <t>EC361</t>
+  </si>
+  <si>
+    <t>Introduction to 5G</t>
+  </si>
+  <si>
+    <t>DS351</t>
+  </si>
+  <si>
+    <t>Statistics for Health Technology</t>
+  </si>
+  <si>
+    <t>DS452</t>
+  </si>
+  <si>
+    <t>Advanced Optimization Techniques</t>
+  </si>
+  <si>
+    <t>ASD353</t>
+  </si>
+  <si>
+    <t>Quantum Hardware and Systems + Quantum Hardware Physics</t>
+  </si>
+  <si>
+    <t>DS358</t>
+  </si>
+  <si>
+    <t>Deep Speech Processing</t>
+  </si>
+  <si>
+    <t>DA353</t>
+  </si>
+  <si>
+    <t>Cloud Computing and AI Services</t>
+  </si>
+  <si>
+    <t>CS373</t>
+  </si>
+  <si>
+    <t>DevSecOps</t>
+  </si>
+  <si>
+    <t>DS357</t>
+  </si>
+  <si>
+    <t>Large Language Models</t>
+  </si>
+  <si>
+    <t>DA354</t>
+  </si>
+  <si>
+    <t>Federated Learning</t>
+  </si>
+  <si>
+    <t>DA355</t>
+  </si>
+  <si>
+    <t>Mathematics for Modern Application</t>
+  </si>
+  <si>
+    <t>DS308</t>
+  </si>
+  <si>
+    <t>Data Security and Privacy</t>
+  </si>
+  <si>
+    <t>F050</t>
+  </si>
+  <si>
+    <t>10 (14.0hr)</t>
+  </si>
+  <si>
+    <t>EC307</t>
+  </si>
+  <si>
+    <t>Wireless Communication</t>
+  </si>
+  <si>
+    <t>F012</t>
   </si>
   <si>
     <t>3 (4.5hr)</t>
-  </si>
-  <si>
-    <t>Hardware</t>
-  </si>
-  <si>
-    <t>CS105</t>
-  </si>
-  <si>
-    <t>Networks</t>
-  </si>
-  <si>
-    <t>F05</t>
-  </si>
-  <si>
-    <t>4 (5.5hr)</t>
   </si>
 </sst>
 </file>
@@ -276,7 +436,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -290,7 +450,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9370DB"/>
+        <fgColor rgb="FFDDA0DD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6347"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFDFBA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF87CEEB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE1FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFBAE1"/>
       </patternFill>
     </fill>
     <fill>
@@ -305,12 +490,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF6347"/>
+        <fgColor rgb="FFFFA07A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFB3BA"/>
+        <fgColor rgb="FFE2BAFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98FB98"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFBA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAFFCB"/>
       </patternFill>
     </fill>
   </fills>
@@ -333,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -359,11 +559,34 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -703,7 +926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -729,10 +952,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -743,12 +966,26 @@
         <v>6</v>
       </c>
       <c r="B3" s="2">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -769,212 +1006,212 @@
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="5" t="s">
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>23</v>
       </c>
+      <c r="G2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>27</v>
+      <c r="D3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>35</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>36</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -994,212 +1231,212 @@
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>19</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>34</v>
+      <c r="E2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>35</v>
+        <v>21</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>36</v>
+        <v>21</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>23</v>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>40</v>
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1447,232 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="11" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" ht="25" customHeight="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1222,122 +1684,538 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" t="s">
         <v>57</v>
       </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
       <c r="E4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" t="s">
         <v>61</v>
       </c>
-      <c r="B5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" t="s">
-        <v>63</v>
-      </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
         <v>66</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D7" t="s">
         <v>67</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>68</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B8" t="s">
         <v>69</v>
       </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>20</v>
+      <c r="D8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="D24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D27" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>109</v>
+      </c>
+      <c r="B28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s">
+        <v>112</v>
+      </c>
+      <c r="D29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
